--- a/jogos_2025-04-01.xlsx
+++ b/jogos_2025-04-01.xlsx
@@ -1149,32 +1149,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
         <v>3.1</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.22</v>
       </c>
-      <c r="X6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45748.5</v>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,65 +1314,65 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
         <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45748.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="Z10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['20', '35', '85']</t>
+          <t>['22', '56']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['83', '90+6']</t>
+          <t>['9005']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45748.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>2.94</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.9</v>
+        <v>2.37</v>
       </c>
       <c r="O12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['20', '35', '85']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['83', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.1</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['22', '56']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['9005']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45748.58333333334</v>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="N16" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
         <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AI16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['37', '78']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.61</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45748.64583333334</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
         <v>2.25</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2667,20 +2667,20 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['37', '78']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45748.64583333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="Q18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI18" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['11', '32']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45748.65625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.33</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['53', '55', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.35</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45748.65625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2.86</v>
       </c>
       <c r="M20" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.8</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['14', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '65']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45748.65625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.94</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
-        <v>3.61</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
@@ -3153,50 +3153,50 @@
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45748.65625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.33</v>
+        <v>3.87</v>
       </c>
       <c r="N22" t="n">
-        <v>2.69</v>
+        <v>2.19</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['12', '32', '49']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['22', '29', '42', '90+7']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['33', '58', '75']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['61', '78']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
         <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45748.65625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['22', '74']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.15</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['66', '74']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45748.65625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2.55</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45748.65625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="Y25" t="n">
         <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['3', '57']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45748.65625</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.82</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>3.87</v>
+        <v>4.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.19</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.62</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['12', '32', '49']</t>
+          <t>['2', '59', '71']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['22', '29', '42', '90+7']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.42</v>
+        <v>2.92</v>
       </c>
       <c r="AI26" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45748.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.71</v>
+        <v>3.47</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.57</v>
       </c>
       <c r="N27" t="n">
-        <v>2.57</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['40', '47']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['4', '57']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45748.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.69</v>
+        <v>2.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['13', '81']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45748.65625</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.87</v>
+        <v>3.17</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="N29" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
         <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['60', '64']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['22', '74']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45748.65625</v>
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.73</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.73</v>
       </c>
       <c r="N30" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['25', '50', '72']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI30" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45748.65625</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2.05</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AJ31" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['13', '81']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45748.65625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Loughgall</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
         <v>2</v>
       </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
         <v>4.4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P32" t="n">
         <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['37', '73']</t>
+          <t>['13', '41', '45', '63', '67']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['55', '74']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45748.65625</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q33" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
         <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X33" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['22', '65']</t>
+          <t>['29', '84', '88']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45748.65625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="T34" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="U34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.36</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X34" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['25', '50', '72']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AH34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI34" t="n">
         <v>2.1</v>
       </c>
-      <c r="AI34" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45748.65625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
         <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
         <v>3.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['37', '73']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['29', '84', '88']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45748.65625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,23 +5029,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Loughgall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>3</v>
-      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.39</v>
+        <v>2.47</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['11', '32']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['13', '41', '45', '63', '67']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['55', '74']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45748.65625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O37" t="n">
+      <c r="Y37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z37" t="n">
         <v>1.8</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>7</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2</v>
-      </c>
       <c r="AA37" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC37" t="n">
         <v>1.91</v>
       </c>
       <c r="AD37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['2', '59', '71']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45748.65625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['40', '47']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['4', '57']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45748.65625</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.66</v>
+        <v>2.71</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA39" t="n">
         <v>4.5</v>
       </c>
-      <c r="O39" t="n">
+      <c r="AB39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI39" t="n">
         <v>2.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['53', '55', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45748.65625</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,20 +5545,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="M40" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O40" t="n">
         <v>3.1</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.23</v>
-      </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="T40" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="U40" t="n">
         <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W40" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X40" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['3', '57']</t>
+          <t>['33', '58', '75']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['61', '78']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45748.65625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.42</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.37</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>2.52</v>
       </c>
       <c r="O41" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['90', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>4</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45748.65625</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="N42" t="n">
-        <v>3.38</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
         <v>1.33</v>
@@ -5853,7 +5853,7 @@
         <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
         <v>1.48</v>
@@ -5862,50 +5862,50 @@
         <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['16', '84']</t>
+          <t>['66', '74']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['18', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45748.65625</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5950,7 +5950,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O43" t="n">
         <v>2.75</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>2.35</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45748.65625</v>
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N44" t="n">
         <v>4</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S44" t="n">
         <v>3.2</v>
       </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['73', '81']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['9', '62', '85', '90']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI44" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45748.65625</v>
@@ -6190,22 +6190,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="N45" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="T45" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V45" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['14', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
         <v>1.38</v>
       </c>
-      <c r="X45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['90', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45748.65625</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,74 +6345,74 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="M46" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>3.2</v>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T46" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U46" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
         <v>1.05</v>
       </c>
       <c r="W46" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X46" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD46" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '62', '85', '90']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH46" t="n">
         <v>1.45</v>
@@ -6421,7 +6421,7 @@
         <v>2.05</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45748.65625</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.17</v>
+        <v>1.99</v>
       </c>
       <c r="M47" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N47" t="n">
-        <v>2.11</v>
+        <v>3.38</v>
       </c>
       <c r="O47" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U47" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V47" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC47" t="n">
         <v>1.62</v>
@@ -6532,25 +6532,25 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['60', '64']</t>
+          <t>['16', '84']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['18', '90']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45748.65625</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,22 +6603,22 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>7.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>1.38</v>
       </c>
       <c r="O48" t="n">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>1.4</v>
@@ -6636,50 +6636,50 @@
         <v>1.05</v>
       </c>
       <c r="W48" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X48" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '85']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45748.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,22 +6732,22 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7.2</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>1.38</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
-        <v>7.5</v>
+        <v>2.88</v>
       </c>
       <c r="P49" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="R49" t="n">
         <v>1.4</v>
@@ -6765,50 +6765,50 @@
         <v>1.05</v>
       </c>
       <c r="W49" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X49" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['3', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AI49" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45748.66666666666</v>
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>2.94</v>
       </c>
       <c r="M53" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="N53" t="n">
-        <v>3.74</v>
+        <v>2.59</v>
       </c>
       <c r="O53" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="S53" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="T53" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="V53" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W53" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="X53" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="Y53" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['9', '24', '57']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['38', '63', '84']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['26', '48', '84']</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45748.89583333334</v>
@@ -7351,22 +7351,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.94</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="N54" t="n">
-        <v>2.59</v>
+        <v>3.74</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="P54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z54" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T54" t="n">
-        <v>4</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AA54" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['9', '24', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['38', '63', '84']</t>
+          <t>['26', '48', '84']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AI54" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45748.89583333334</v>
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="M55" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="N55" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="O55" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P55" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T55" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="X55" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.61</v>
       </c>
-      <c r="AA55" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI55" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45748.95833333334</v>
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="M56" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="N56" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="O56" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y56" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2</v>
-      </c>
       <c r="Z56" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.32</v>
+        <v>5.15</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AC56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI56" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ56" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45748.95833333334</v>
